--- a/research/traditional_assets/database/data/luxembourg/luxembourg_coal_related_energy.xlsx
+++ b/research/traditional_assets/database/data/luxembourg/luxembourg_coal_related_energy.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.435</v>
+        <v>-0.408</v>
       </c>
       <c r="G2">
-        <v>-0.9090909090909092</v>
+        <v>-0.6875</v>
       </c>
       <c r="H2">
-        <v>-0.9090909090909092</v>
+        <v>-0.6875</v>
       </c>
       <c r="I2">
-        <v>-1.454545454545455</v>
+        <v>-0.41375</v>
       </c>
       <c r="J2">
-        <v>-1.433068181818182</v>
+        <v>-0.2812684729064039</v>
       </c>
       <c r="K2">
-        <v>50.6</v>
+        <v>2.93</v>
       </c>
       <c r="L2">
-        <v>41.81818181818182</v>
+        <v>1.83125</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -633,70 +633,67 @@
         <v>0.003</v>
       </c>
       <c r="V2">
-        <v>9.646302250803858e-05</v>
+        <v>0.0001704545454545454</v>
       </c>
       <c r="W2">
-        <v>-1.258706467661691</v>
+        <v>0.4277372262773723</v>
       </c>
       <c r="X2">
-        <v>0.0621131098795048</v>
+        <v>0.1300234656889993</v>
       </c>
       <c r="Y2">
-        <v>-1.320819577541196</v>
+        <v>0.297713760588373</v>
       </c>
       <c r="Z2">
-        <v>0.04290780141843971</v>
+        <v>0.02444688913335778</v>
       </c>
       <c r="AA2">
-        <v>-0.061489804964539</v>
+        <v>-0.006876139173851703</v>
       </c>
       <c r="AB2">
-        <v>0.06281930165094005</v>
+        <v>0.12785532499406</v>
       </c>
       <c r="AC2">
-        <v>-0.124309106615479</v>
+        <v>-0.1347314641679117</v>
       </c>
       <c r="AD2">
-        <v>3.19</v>
+        <v>3.21</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>3.19</v>
+        <v>3.21</v>
       </c>
       <c r="AG2">
-        <v>3.187</v>
+        <v>3.207</v>
       </c>
       <c r="AH2">
-        <v>0.09303003791192768</v>
+        <v>0.154252763094666</v>
       </c>
       <c r="AI2">
-        <v>0.4596541786743516</v>
+        <v>0.5071090047393365</v>
       </c>
       <c r="AJ2">
-        <v>0.09295068101612856</v>
+        <v>0.1541308213581968</v>
       </c>
       <c r="AK2">
-        <v>0.4594204987746865</v>
+        <v>0.5068752963489805</v>
       </c>
       <c r="AL2">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AM2">
-        <v>0.33</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="AN2">
-        <v>-4.387895460797799</v>
-      </c>
-      <c r="AO2">
-        <v>-5.333333333333333</v>
+        <v>78.29268292682926</v>
       </c>
       <c r="AP2">
-        <v>-4.383768913342504</v>
+        <v>78.21951219512195</v>
       </c>
       <c r="AQ2">
-        <v>-5.333333333333333</v>
+        <v>73.55555555555557</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +713,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.435</v>
+        <v>-0.408</v>
       </c>
       <c r="G3">
-        <v>-0.9090909090909092</v>
+        <v>-0.6875</v>
       </c>
       <c r="H3">
-        <v>-0.9090909090909092</v>
+        <v>-0.6875</v>
       </c>
       <c r="I3">
-        <v>-1.454545454545455</v>
+        <v>-0.41375</v>
       </c>
       <c r="J3">
-        <v>-1.433068181818182</v>
+        <v>-0.2812684729064039</v>
       </c>
       <c r="K3">
-        <v>50.6</v>
+        <v>2.93</v>
       </c>
       <c r="L3">
-        <v>41.81818181818182</v>
+        <v>1.83125</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -761,70 +758,67 @@
         <v>0.003</v>
       </c>
       <c r="V3">
-        <v>9.646302250803858e-05</v>
+        <v>0.0001704545454545454</v>
       </c>
       <c r="W3">
-        <v>-1.258706467661691</v>
+        <v>0.4277372262773723</v>
       </c>
       <c r="X3">
-        <v>0.0621131098795048</v>
+        <v>0.1300234656889993</v>
       </c>
       <c r="Y3">
-        <v>-1.320819577541196</v>
+        <v>0.297713760588373</v>
       </c>
       <c r="Z3">
-        <v>0.04290780141843971</v>
+        <v>0.02444688913335778</v>
       </c>
       <c r="AA3">
-        <v>-0.061489804964539</v>
+        <v>-0.006876139173851703</v>
       </c>
       <c r="AB3">
-        <v>0.06281930165094005</v>
+        <v>0.12785532499406</v>
       </c>
       <c r="AC3">
-        <v>-0.124309106615479</v>
+        <v>-0.1347314641679117</v>
       </c>
       <c r="AD3">
-        <v>3.19</v>
+        <v>3.21</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>3.19</v>
+        <v>3.21</v>
       </c>
       <c r="AG3">
-        <v>3.187</v>
+        <v>3.207</v>
       </c>
       <c r="AH3">
-        <v>0.09303003791192768</v>
+        <v>0.154252763094666</v>
       </c>
       <c r="AI3">
-        <v>0.4596541786743516</v>
+        <v>0.5071090047393365</v>
       </c>
       <c r="AJ3">
-        <v>0.09295068101612856</v>
+        <v>0.1541308213581968</v>
       </c>
       <c r="AK3">
-        <v>0.4594204987746865</v>
+        <v>0.5068752963489805</v>
       </c>
       <c r="AL3">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>0.33</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="AN3">
-        <v>-4.387895460797799</v>
-      </c>
-      <c r="AO3">
-        <v>-5.333333333333333</v>
+        <v>78.29268292682926</v>
       </c>
       <c r="AP3">
-        <v>-4.383768913342504</v>
+        <v>78.21951219512195</v>
       </c>
       <c r="AQ3">
-        <v>-5.333333333333333</v>
+        <v>73.55555555555557</v>
       </c>
     </row>
   </sheetData>
